--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -154,7 +154,7 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -184,7 +184,7 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -194,7 +194,7 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J29" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="0">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="L29" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N29" t="inlineStr" s="0">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="P29" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: admin cleanup-branches dry-run listed merged branches (24 skipped, 0 deleted) without mutating.</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="J35" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="0">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="L35" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N35" t="inlineStr" s="0">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="P35" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: skills add/list/install/remove round-tripped; install created per-backend symlinks (.claude/.codex/.opencode/.kiro/.agents).</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -9771,8 +9771,102 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t>RUN-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-016</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="0">
+        <is>
+          <t>skills add/list/install/remove in isolated AGEND_HOME</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="0">
+        <is>
+          <t>Skill round-trips + per-backend install</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="0">
+        <is>
+          <t>Symlinks created at 5 backend paths; remove idempotent</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="0">
+        <is>
+          <t>console capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t>RUN-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-010</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t>admin cleanup-branches (dry-run) against source repo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="0">
+        <is>
+          <t>Preview-only, no deletions</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="0">
+        <is>
+          <t>24 branches evaluated, 0 deleted (dry-run); audit log written then cleaned</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="0">
+        <is>
+          <t>console capture</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I8"/>
 </worksheet>
 </file>
 

--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -154,7 +154,7 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -184,7 +184,7 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <v>43</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -194,7 +194,7 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <v>44</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <v>43</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -239,7 +239,7 @@
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>Inventory done; representative testing done; 1 logistical bug fixed + retested; 1 UX item deferred</t>
+          <t>Inventory done; broad code/API/TUI testing done; 2 logistical/UX bugs fixed + retested; 21 stories remain untested or environment-gated</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="0">
@@ -607,12 +607,12 @@
       </c>
       <c r="L3" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N3" t="inlineStr" s="0">
@@ -627,7 +627,7 @@
       </c>
       <c r="P3" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: cargo test --bin agend-terminal channel:: / channel::telegram / notification_queue passed, covering channel binding, Telegram adapter, auth, dedup, caps, and notification UX.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="0">
@@ -689,12 +689,12 @@
       </c>
       <c r="L4" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N4" t="inlineStr" s="0">
@@ -709,7 +709,7 @@
       </c>
       <c r="P4" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: cargo test --bin agend-terminal daemon::ci_watch and daemon::pr_state passed, covering CI watch and PR-state behaviours.</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="J5" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" t="inlineStr" s="0">
@@ -771,12 +771,12 @@
       </c>
       <c r="L5" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N5" t="inlineStr" s="0">
@@ -791,7 +791,7 @@
       </c>
       <c r="P5" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: MCP send/inbox/task smoke tests passed and channel/notification queues passed.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J6" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" t="inlineStr" s="0">
@@ -853,12 +853,12 @@
       </c>
       <c r="L6" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N6" t="inlineStr" s="0">
@@ -873,7 +873,7 @@
       </c>
       <c r="P6" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: runtime_config, mcp_config, and fleet tests passed.</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="J7" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" t="inlineStr" s="0">
@@ -935,12 +935,12 @@
       </c>
       <c r="L7" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N7" t="inlineStr" s="0">
@@ -955,7 +955,7 @@
       </c>
       <c r="P7" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: decision post/list smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="J9" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" t="inlineStr" s="0">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L9" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N9" t="inlineStr" s="0">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P9" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: daemon::dispatch_idle tests passed.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J10" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="0">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="L10" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N10" t="inlineStr" s="0">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="P10" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: fleet:: tests passed (83 passed, 1 ignored).</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="J11" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="0">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="L11" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N11" t="inlineStr" s="0">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="P11" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: health:: and daemon::idle_watchdog tests passed; health MCP smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="J12" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="0">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="L12" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N12" t="inlineStr" s="0">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="P12" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: quickstart --unattended smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="J13" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="0">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="L13" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N13" t="inlineStr" s="0">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="P13" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: schedules and deployments tests passed; schedule/deployment MCP smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="J15" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" t="inlineStr" s="0">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="L15" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N15" t="inlineStr" s="0">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="P15" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: skills CLI add/list/install/remove smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J16" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" t="inlineStr" s="0">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L16" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N16" t="inlineStr" s="0">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P16" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: tasks:: and task_events tests passed; task MCP smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J17" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="0">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="L17" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N17" t="inlineStr" s="0">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="P17" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: teams:: tests passed; team MCP list smoke passed.</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="J18" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" t="inlineStr" s="0">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="L18" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N18" t="inlineStr" s="0">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="P18" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: TUI keybind/layout/mouse/overlay/session/command tests passed.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="J19" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" t="inlineStr" s="0">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="L19" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N19" t="inlineStr" s="0">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="P19" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: worktree and binding tests passed; worktree MCP smoke exercised release/binding_state/gc.</t>
         </is>
       </c>
     </row>
@@ -2975,22 +2975,22 @@
       </c>
       <c r="J32" t="inlineStr" s="0">
         <is>
-          <t>Pass</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="0">
         <is>
-          <t>ERR-001: verify --quick 'instructions' probe always reported claude=false (checked stale .claude/rules/agend.md path that migration deletes).</t>
+          <t/>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="0">
         <is>
-          <t>Done</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="0">
         <is>
-          <t>Pass</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N32" t="inlineStr" s="0">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="P32" t="inlineStr" s="0">
         <is>
-          <t>TEST: After fix, verify --quick reports passed=5 failed=0.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="K33" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-001: verify --quick 'instructions' probe always reported claude=false (checked stale .claude/rules/agend.md path that migration deletes).</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="0">
         <is>
-          <t>N/A</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="0">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P33" t="inlineStr" s="0">
         <is>
-          <t>TEST: service status returned not_installed (non-destructive).</t>
+          <t>TEST: After fix, verify --quick reports passed=5 failed=0.</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="P34" t="inlineStr" s="0">
         <is>
-          <t>TEST: doctor providers --format json returned structured provider descriptor.</t>
+          <t>TEST: service status returned not_installed (non-destructive).</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="P35" t="inlineStr" s="0">
         <is>
-          <t>TEST: skills add/list/install/remove round-tripped; install created per-backend symlinks (.claude/.codex/.opencode/.kiro/.agents).</t>
+          <t>TEST: doctor providers --format json returned structured provider descriptor.</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="P36" t="inlineStr" s="0">
         <is>
-          <t>TEST: quickstart --unattended created fleet.yaml idempotently in empty AGEND_HOME.</t>
+          <t>TEST: skills add/list/install/remove round-tripped; install created per-backend symlinks (.claude/.codex/.opencode/.kiro/.agents).</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3390,17 @@
       </c>
       <c r="K37" t="inlineStr" s="0">
         <is>
-          <t>ERR-002 (minor/UX): bugreport writes bugreport-*.txt into CWD, not $AGEND_HOME — clutters whatever dir it is run from.</t>
+          <t/>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="0">
         <is>
-          <t>Deferred</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N37" t="inlineStr" s="0">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="P37" t="inlineStr" s="0">
         <is>
-          <t>TEST: Behaviour confirmed; redaction path present. Output-location UX noted, not yet changed.</t>
+          <t>TEST: quickstart --unattended created fleet.yaml idempotently in empty AGEND_HOME.</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3472,12 @@
       </c>
       <c r="K38" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-002 (minor/UX): bugreport wrote bugreport-*.txt into CWD, cluttering whatever dir it was run from.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="0">
         <is>
-          <t>N/A</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="0">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="P38" t="inlineStr" s="0">
         <is>
-          <t>TEST: completions bash/zsh/fish all produced non-empty scripts.</t>
+          <t>TEST: Fixed: bugreport now writes under AGEND_HOME/bugreports; red test failed before impl and passes after fix.</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="J39" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="0">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="L39" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N39" t="inlineStr" s="0">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="P39" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: completions bash/zsh/fish all produced non-empty scripts.</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J79" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="0">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L79" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N79" t="inlineStr" s="0">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="P79" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo test --bin agend-terminal keybinds + layout:: passed.</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="J80" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="0">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L80" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N80" t="inlineStr" s="0">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P80" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: layout::, app::dispatch, and keybinds tests passed for split/focus/zoom/move actions.</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="J81" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="0">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L81" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N81" t="inlineStr" s="0">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="P81" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: app::tui_events and keybinds tests passed for scroll-mode dispatch.</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="J82" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="0">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="L82" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N82" t="inlineStr" s="0">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="P82" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: app::overlay and app::tui_events tests passed for panels/overlays.</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="J83" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="0">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="L83" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N83" t="inlineStr" s="0">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="P83" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo test --bin agend-terminal app::mouse passed (27 tests).</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="J84" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="0">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L84" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N84" t="inlineStr" s="0">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="P84" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: keybinds and image_paste tests passed.</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="J85" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="0">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="L85" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N85" t="inlineStr" s="0">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P85" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo test --bin agend-terminal app::commands passed (16 tests).</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="J86" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="0">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L86" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N86" t="inlineStr" s="0">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P86" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo test --bin agend-terminal app::session passed (12 tests).</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="J87" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="0">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="L87" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N87" t="inlineStr" s="0">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="P87" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: daemon::ticker, daemon::per_tick, and daemon::cron_tick tests passed.</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="J88" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="0">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L88" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N88" t="inlineStr" s="0">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="P88" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: daemon::supervisor and daemon::crash_respawn tests passed.</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="J89" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="0">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="L89" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N89" t="inlineStr" s="0">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="P89" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: backend tests passed (125 passed, 3 ignored).</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="J90" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="0">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="L90" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N90" t="inlineStr" s="0">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="P90" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: state:: and behavioral tests passed.</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="J91" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="0">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L91" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N91" t="inlineStr" s="0">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="P91" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: channel:: and channel::telegram tests passed.</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="J92" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="0">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="L92" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N92" t="inlineStr" s="0">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="P92" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: notification_queue tests passed.</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J93" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="0">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="L93" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N93" t="inlineStr" s="0">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="P93" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: fleet:: tests passed.</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="J94" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="0">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L94" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N94" t="inlineStr" s="0">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="P94" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: runtime_config tests passed.</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="J95" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="0">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="L95" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N95" t="inlineStr" s="0">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="P95" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: mcp_config tests passed.</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="J96" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="0">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="L96" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N96" t="inlineStr" s="0">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P96" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: worktree and binding tests passed.</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="J97" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="0">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="L97" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N97" t="inlineStr" s="0">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P97" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo test --bin agend-git passed (85 tests).</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="J98" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="0">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="L98" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N98" t="inlineStr" s="0">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P98" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: daemon::ci_watch and daemon::pr_state tests passed.</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="J99" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="0">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="L99" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N99" t="inlineStr" s="0">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="P99" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: tasks:: and task_events tests passed.</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="J100" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="0">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="L100" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N100" t="inlineStr" s="0">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="P100" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: decision MCP smoke passed.</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="J101" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="0">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="L101" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N101" t="inlineStr" s="0">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="P101" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: schedules and deployments tests passed.</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="J102" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="0">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="L102" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N102" t="inlineStr" s="0">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="P102" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: daemon::retention tests passed.</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="J103" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="0">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="L103" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N103" t="inlineStr" s="0">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="P103" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: auth_cookie and config_integrity tests passed.</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J104" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="0">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="L104" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N104" t="inlineStr" s="0">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="P104" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: api::tests and api::request_dedup tests passed.</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="J106" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="0">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="L106" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N106" t="inlineStr" s="0">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="P106" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: bugreport red/green tests passed; diagnostics command smoke passed.</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-013</t>
+          <t>US-CLI-014</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-018</t>
+          <t>US-CLI-019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="0">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t>Deferred</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="0">
         <is>
-          <t>Candidate: default output under $AGEND_HOME or a configurable --out path. Not changed this pass to keep the fix surface minimal and reviewed.</t>
+          <t>src/bugreport.rs now writes to AGEND_HOME/bugreports/ and creates that directory. English/zh-TW CLI + diagnostics docs updated.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Red test-only commit failed as expected (wrote into CWD); post-fix cargo test --test cli_smoke bugreport_writes_with_valid_home passed and direct smoke wrote only under AGEND_HOME/bugreports/.</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-013</t>
+          <t>US-CLI-014</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-019/014/015/017/018</t>
+          <t>US-CLI-020/015/016/018/019</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-013</t>
+          <t>US-CLI-014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="0">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t>US-CLI-016</t>
+          <t>US-CLI-017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
@@ -9865,8 +9865,196 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t>RUN-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-019</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="0">
+        <is>
+          <t>bugreport red/green regression</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="0">
+        <is>
+          <t>Bugreport writes under AGEND_HOME/bugreports and not CWD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="0">
+        <is>
+          <t>test-only commit failed; implementation commit passed cli_smoke + bin bugreport tests</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --test cli_smoke bugreport_writes_with_valid_home; cargo test --bin agend-terminal bugreport</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t>RUN-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t>US-TUI-001..008</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="0">
+        <is>
+          <t>TUI unit/dispatcher tests</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="0">
+        <is>
+          <t>Keyboard, mouse, overlay, command, layout, session, image-paste behaviours pass</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="0">
+        <is>
+          <t>keybinds 19; commands 16; mouse 27; session 12; layout 59; tui_events 13; overlay 14; image_paste 9 all passed</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --bin agend-terminal &lt;filters&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t>RUN-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t>US-DOC/SYS channel/config/worktree/task/daemon rows</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="0">
+        <is>
+          <t>Subsystem cargo-test batches</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="0">
+        <is>
+          <t>Subsystem invariants pass</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="0">
+        <is>
+          <t>channel 195; ci_watch 226; pr_state 91; worktree 238; binding 53; tasks 163; task_events 49; schedules 33; deployments 55; teams 34; health 53; daemon/per_tick/ticker/supervisor batches passed</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --bin agend-terminal &lt;filters&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t>RUN-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t>US-SYS-011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="0">
+        <is>
+          <t>agend-git safety tests</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="0">
+        <is>
+          <t>Git shim safeguards pass</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="0">
+        <is>
+          <t>85 passed</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --bin agend-git</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I12"/>
 </worksheet>
 </file>
 

--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -154,7 +154,7 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -164,7 +164,7 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -184,7 +184,7 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -194,7 +194,7 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -239,7 +239,7 @@
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>Inventory done; broad code/API/TUI testing done; 2 logistical/UX bugs fixed + retested; 21 stories remain untested or environment-gated</t>
+          <t>Inventory done; broad code/API/TUI testing done; 3 logistical/UX bugs fixed + retested; remaining stories are interactive/destructive/external-service/feature-gated</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="J2" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="0">
@@ -525,12 +525,12 @@
       </c>
       <c r="L2" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N2" t="inlineStr" s="0">
@@ -545,7 +545,7 @@
       </c>
       <c r="P2" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: attach/inject/list/kill/connect behaviours were exercised in isolated daemon smoke tests.</t>
         </is>
       </c>
     </row>
@@ -2401,22 +2401,22 @@
       </c>
       <c r="J25" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-004: failed connect registered an external agent before backend spawn and left a stale connected entry when spawn failed.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N25" t="inlineStr" s="0">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P25" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: Fixed: connect deregisters external agent on spawn error; red regression test failed before impl and passes after fix; positive /usr/bin/true connect still passes.</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="J40" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="0">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="L40" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N40" t="inlineStr" s="0">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="P40" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: verify-push --claim-from-stdin --json with known 'deps unchanged' claim returned ok=true and Cargo.lock unchanged.</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -10053,8 +10053,102 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t>RUN-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-006</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="0">
+        <is>
+          <t>connect bad backend red/green regression + positive connect smoke</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="0">
+        <is>
+          <t>Failed backend spawn must not leave stale external agent; valid backend exits cleanly</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="0">
+        <is>
+          <t>red test failed with badext listed; post-fix test passed; /usr/bin/true connect exited 0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --test cli_smoke connect_failed_spawn_deregisters_external_agent; manual isolated daemon smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t>RUN-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-021</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="0">
+        <is>
+          <t>verify-push --claim-from-stdin --json</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="0">
+        <is>
+          <t>Known claim grammar verifies against diff</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="0">
+        <is>
+          <t>deps unchanged -&gt; ok=true, Cargo.lock unchanged</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr" s="0">
+        <is>
+          <t>target/debug/agend-terminal verify-push --base origin/main --head HEAD --claim-from-stdin --json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I14"/>
 </worksheet>
 </file>
 

--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -154,7 +154,7 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -164,7 +164,7 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -174,7 +174,7 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -184,7 +184,7 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -194,7 +194,7 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -239,7 +239,7 @@
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t>Inventory done; broad code/API/TUI testing done; 3 logistical/UX bugs fixed + retested; remaining stories are interactive/destructive/external-service/feature-gated</t>
+          <t>Complete: all 107 stories inventoried + tested; 5 logistical/UX bugs fixed + retested; remaining items are environment-gated (1) with unit-test coverage. Interactive TUI rendering remains operator-verified visually.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="J8" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" t="inlineStr" s="0">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="L8" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N8" t="inlineStr" s="0">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="P8" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: Diagnostics doc components all exercised: doctor providers --format json, bugreport (now AGEND_HOME/bugreports), capture backend + promote. bugreport redaction unit tests pass.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="J14" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="0">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="L14" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N14" t="inlineStr" s="0">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="P14" t="inlineStr" s="0">
         <is>
-          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours.</t>
+          <t>Feature-doc row; lower-level CLI/MCP/TUI rows below track concrete behaviours. | TEST: service install -&gt; status=running -&gt; uninstall -&gt; status=not_installed round-trip in isolated AGEND_HOME; plist created then cleaned, no stray launchd job.</t>
         </is>
       </c>
     </row>
@@ -2073,22 +2073,22 @@
       </c>
       <c r="J21" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-007: `agend-terminal app` panicked (exit 101, 'Device not configured') and leaked raw mouse/alt-screen escape sequences when stdin/stdout was not a TTY.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N21" t="inlineStr" s="0">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="P21" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: Fixed: early IsTerminal guard returns a clean actionable error pointing at `agend-terminal start`. Red test failed (panic) before fix, passes after; manual headless run now exits 1 with a readable message and no escape leak. Interactive TUI itself remains operator-verified visually.</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="J30" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="0">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="L30" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N30" t="inlineStr" s="0">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="P30" t="inlineStr" s="0">
         <is>
-          <t>Do not run destructive zombie cleanup against the live session.</t>
+          <t>Do not run destructive zombie cleanup against the live session. | TEST: admin cleanup-zombies --age 3650d --yes reported no qualifying zombies in isolated AGEND_HOME (non-destructive).</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="J31" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="0">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="L31" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N31" t="inlineStr" s="0">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="P31" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: capture backend --backend codex --seconds 1 spawned codex and captured its VTerm screen, exit 0.</t>
         </is>
       </c>
     </row>
@@ -2975,22 +2975,22 @@
       </c>
       <c r="J32" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-005: capture promote copied &lt;scenario&gt;.raw before appending MANIFEST.yaml (create(false)); a missing manifest left an orphan .raw with no manifest entry.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N32" t="inlineStr" s="0">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="P32" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: Fixed: promote fails fast on missing manifest and rolls back the copy on append failure. Red regression test failed before fix, passes after; happy-path promote with a present manifest appends the entry and writes the .raw.</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="J41" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="0">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L41" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N41" t="inlineStr" s="0">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P41" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: hook-event --instance shell with stdin JSON exited 0 with empty stdout; gracefully dropped event in shadow-mode when no daemon (matches hidden observe-only contract).</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="J43" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="0">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="L43" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N43" t="inlineStr" s="0">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="P43" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: download_attachment returned proper 'No Telegram channel configured' error when no channel is bound.</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="J49" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="0">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="L49" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N49" t="inlineStr" s="0">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="P49" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: start_instance with instance param correctly errors when agent already running; schema/handler both require 'instance'.</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J50" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K50" t="inlineStr" s="0">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="L50" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N50" t="inlineStr" s="0">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="P50" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: replace_instance spawned a fresh instance (spawned=true).</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="J52" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="0">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="L52" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N52" t="inlineStr" s="0">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="P52" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: interrupt returned ok=true for target instance (ESC byte injected).</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="J56" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="0">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="L56" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N56" t="inlineStr" s="0">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="P56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: move_pane returned ok=true relocating the pane to a target tab.</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="J58" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="0">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L58" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N58" t="inlineStr" s="0">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: tui_screenshot correctly errors in daemon-only mode (requires TUI mode) — expected behaviour; covered by screenshot unit test for the SVG path.</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="J62" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="0">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L62" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N62" t="inlineStr" s="0">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="P62" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: restart_daemon self-respawned the isolated test daemon (successor confirmed healthy); list showed the agent afterward.</t>
         </is>
       </c>
     </row>
@@ -6255,22 +6255,22 @@
       </c>
       <c r="J72" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>ERR-006 (env-only, not a product defect): bind_self could not be exercised end-to-end because the agend-git shim blocks all git mutations from this agent-rooted shell (ancestry guard #2158/#2234), so a clean source repo cannot be constructed here.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N72" t="inlineStr" s="0">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="P72" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: MCP handler dispatches and validates (returns structured lease_failed/cross_agent_conflict); binding/worktree_pool unit tests (53+) cover the bind logic.</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="J74" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="0">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="L74" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N74" t="inlineStr" s="0">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="P74" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: force_release_worktree returned a structured binding_outcome (already_released) without mutating non-pool paths.</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="J107" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="0">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="L107" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N107" t="inlineStr" s="0">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="P107" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo check --features tray compiled (tray-icon/tao/muda).</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="J108" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="0">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="L108" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="0">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N108" t="inlineStr" s="0">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="P108" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>TEST: cargo check --features discord compiled (twilight-gateway/http/validate).</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -9469,14 +9469,202 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="0">
+        <is>
+          <t>ERR-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-006</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="0">
+        <is>
+          <t>agend-terminal connect badext --backend /no/such/backend</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="0">
+        <is>
+          <t>connect registered the external agent before spawning the backend. If backend spawn failed, the function returned the spawn error without deregistering, so list --json showed badext as connected even though no backend process existed.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="0">
+        <is>
+          <t>Medium (logistical / stale state)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="0">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="0">
+        <is>
+          <t>src/connect.rs now deregisters the external agent when Command::spawn() fails after registration.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="0">
+        <is>
+          <t>Red regression test failed before impl; post-fix cargo test --test cli_smoke connect_failed_spawn_deregisters_external_agent passed. Positive /usr/bin/true connect smoke still exits 0 and deregisters normally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t>ERR-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-013</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="0">
+        <is>
+          <t>agend-terminal capture promote &lt;cap&gt; &lt;name&gt; --scenario-kind real_capture (run outside project root)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="0">
+        <is>
+          <t>promote copied &lt;scenario&gt;.raw to tests/fixtures/state-replay/ BEFORE appending the entry to MANIFEST.yaml (opened with create(false)). When the manifest was absent the append failed but the orphan .raw was left behind — a half-promoted fixture the replay harness would not discover.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="0">
+        <is>
+          <t>Medium (logistical / orphan state)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="0">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="0">
+        <is>
+          <t>src/capture.rs: fail fast with an actionable error when the manifest is missing (before any copy), and roll back the copied .raw if the append itself fails.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="0">
+        <is>
+          <t>Red regression test (promote_missing_manifest_errors_and_leaves_no_orphan_raw) failed on prior impl, passes after fix; CLI smoke confirms no orphan on missing manifest and a clean append on the happy path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t>ERR-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t>US-MCP-031</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t>MCP bind_self against a freshly constructed git repo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="0">
+        <is>
+          <t>Could not exercise bind_self end-to-end in this environment: the agend-git PATH shim denies all git mutations originating from this agent-rooted shell (process-ancestry guard #2158/#2234), so a clean source repo with an origin remote cannot be built here. This is the harness/environment guard working as designed, NOT a product defect.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="0">
+        <is>
+          <t>Info (environment-gated)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="0">
+        <is>
+          <t>Won't Fix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="0">
+        <is>
+          <t>Documented; bind logic is covered by binding/worktree_pool unit tests and the MCP handler returns structured lease_failed/cross_agent_conflict errors.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="0">
+        <is>
+          <t>Re-confirmed the shim guard fires deterministically; MCP handler dispatch + validation path exercised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t>ERR-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t>agend-terminal app with non-TTY stdin/stdout (piped/headless)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t>app called ratatui::init() unconditionally; without a TTY it panicked (exit 101, 'Device not configured') AFTER already emitting raw mouse/alt-screen escape sequences to the captured stream.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="0">
+        <is>
+          <t>Medium (UX / crash + terminal corruption)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="0">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="0">
+        <is>
+          <t>src/app/mod.rs: early IsTerminal guard returns a clean actionable error (use `agend-terminal start` for headless) before any terminal mutation.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="0">
+        <is>
+          <t>Red regression test (app_without_tty_errors_cleanly_not_panic) panicked before fix, passes after; manual headless run now exits 1 with a readable message and no escape-sequence leak.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I21"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -10147,8 +10335,337 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>RUN-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t>US-MCP-008/009/011/015/017/033</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="0">
+        <is>
+          <t>MCP lifecycle + worktree tools via bridge</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="0">
+        <is>
+          <t>Each tool dispatches and returns valid payload/expected error</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="0">
+        <is>
+          <t>create/replace/start/interrupt/move_pane/force_release all returned expected results; tui_screenshot correctly errors in daemon mode</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr" s="0">
+        <is>
+          <t>agend-mcp-bridge stdio capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
+          <t>RUN-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t>US-MCP-021</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="0">
+        <is>
+          <t>restart_daemon on isolated test daemon</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="0">
+        <is>
+          <t>Daemon self-respawns and remains usable</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="0">
+        <is>
+          <t>successor confirmed healthy; list showed agent; stop clean</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr" s="0">
+        <is>
+          <t>bridge + list/stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="0">
+        <is>
+          <t>RUN-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-011/012/022</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="0">
+        <is>
+          <t>cleanup-zombies / capture backend / hook-event</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr" s="0">
+        <is>
+          <t>Each command behaves correctly and non-destructively</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr" s="0">
+        <is>
+          <t>no zombies reported; codex VTerm captured; hook-event exit 0 empty stdout shadow-drop</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr" s="0">
+        <is>
+          <t>console capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t>RUN-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-013</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="0">
+        <is>
+          <t>capture promote red/green + CLI smoke</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="0">
+        <is>
+          <t>Missing manifest must not orphan .raw; happy path appends</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="0">
+        <is>
+          <t>red test failed pre-fix; post-fix 11/11 capture tests pass; CLI smoke shows no orphan + clean append</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --bin agend-terminal capture::tests::promote; CLI smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t>RUN-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t>US-DOC-013</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="0">
+        <is>
+          <t>service install/status/uninstall round-trip</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="0">
+        <is>
+          <t>Idempotent user-service lifecycle, cleaned up</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="0">
+        <is>
+          <t>not_installed -&gt; running -&gt; not_installed; plist created then removed; no stray launchd job</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr" s="0">
+        <is>
+          <t>console capture + launchctl/ls checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t>RUN-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t>US-SYS-021/022</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="0">
+        <is>
+          <t>cargo check --features tray / discord</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="0">
+        <is>
+          <t>Feature-gated builds compile</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="0">
+        <is>
+          <t>both finished OK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr" s="0">
+        <is>
+          <t>cargo check --features &lt;feat&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t>RUN-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t>US-CLI-002</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t>fugu-0acdd8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="0">
+        <is>
+          <t>app without TTY red/green + manual headless run</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="0">
+        <is>
+          <t>app must not panic without a TTY</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="0">
+        <is>
+          <t>red test panicked pre-fix; post-fix test passes; manual run exits 1 with clean TTY message</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr" s="0">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr" s="0">
+        <is>
+          <t>cargo test --test cli_smoke app_without_tty_errors_cleanly_not_panic</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I21"/>
 </worksheet>
 </file>
 

--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -102,6 +107,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11003,12 +11009,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>8e89af16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>host_receives_credentials() gates all 3 providers; loopback+SaaS+AGEND_CI_TRUSTED_HOSTS; test credential_gate_blocks_untrusted_hosts; ci_watch 252 + handlers::ci 79 green</t>
         </is>
@@ -11035,9 +11041,19 @@
           <t>MCP authz</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>0013c88e</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>force_release + delete_instance owner/orchestrator ACL (is_orchestrator_of); 2 tests; force_release 23 + instance_state 27 green</t>
         </is>
       </c>
     </row>
@@ -11062,9 +11078,15 @@
           <t>MCP authz</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>repo merge: no instance-ownership model, already CI-green gated; per-caller ACL needs clearer ownership def</t>
         </is>
       </c>
     </row>
@@ -11089,9 +11111,19 @@
           <t>operator gate</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0013c88e</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>operator gate blocks agent config-set of safety keys (progress_mode/idle_watchdog/hang_auto_recovery/usage_limit) in all modes; test + operator_gate 14 green</t>
         </is>
       </c>
     </row>
@@ -11116,9 +11148,19 @@
           <t>spawn env</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>4796de13</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>added NODE_OPTIONS/GIT_SSH_COMMAND/BASH_ENV/ENV/PYTHONSTARTUP/PERL5OPT/RUBYOPT + DYLD framework paths; sensitive_env tests green</t>
         </is>
       </c>
     </row>
@@ -11143,9 +11185,19 @@
           <t>tasks</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>4ca863cc</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>64 KiB metadata_value cap; test metadata_set_rejects_oversized_value_audit2_005; tasks 164 green</t>
         </is>
       </c>
     </row>
@@ -11197,9 +11249,19 @@
           <t>daemon tick</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>423868d6</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>catch_unwind around AgentExitEvent match (mirror #1002); supervisor 99 + crash_respawn 4 green</t>
         </is>
       </c>
     </row>
@@ -11224,9 +11286,19 @@
           <t>daemon recovery</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>6b57fa8c</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>last_stage2_notify_at backoff (5min); reset on success; recovery_dispatcher 23 + health 53 green</t>
         </is>
       </c>
     </row>
@@ -11251,9 +11323,15 @@
           <t>ci_watch poller</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Needs per-sha-aggregate-change (or per-workflow) dedup redesign in select_runs_to_notify — load-bearing CI path, high regression risk; deferred for dedicated work + poller_tests coverage</t>
         </is>
       </c>
     </row>
@@ -11278,9 +11356,19 @@
           <t>schedules</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>5e97aba3</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>is_due_in_tz UTC-bounded window; repro 180-&gt;2 fires; test ny_dst_fall_back_fold_hour...; cron_tick 30 + schedules 29 green</t>
         </is>
       </c>
     </row>
@@ -11305,9 +11393,19 @@
           <t>tasks/api</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>2ac643f8</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>messaging.rs mints t-&lt;ts&gt;-&lt;pid&gt;-&lt;seq&gt;; guard widened to both mint sites; tasks::handler 27 + messaging 55 green</t>
         </is>
       </c>
     </row>
@@ -11332,9 +11430,19 @@
           <t>runtime_config</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>26f960ca</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>set() file-locked + store::atomic_write; runtime_config 15 green</t>
         </is>
       </c>
     </row>
@@ -11359,9 +11467,19 @@
           <t>skills</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>59d13098</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>per-digest flock in stage_filtered_source; digest path + GC unchanged; skills 31 green</t>
         </is>
       </c>
     </row>
@@ -11413,9 +11531,19 @@
           <t>inbox/task_events</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>1fe40700</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>store::fsync_parent_dir helper + applied at inbox/storage (4) + task_events; disk.rs via atomic_write; inbox 176 + task_events 49 green</t>
         </is>
       </c>
     </row>
@@ -11440,9 +11568,19 @@
           <t>TUI layout</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>73cfdd19</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>close_tab active&gt;idx decrement; test close_tab_left_of_active_keeps_focus_audit2_016; layout 60 green</t>
         </is>
       </c>
     </row>
@@ -11467,9 +11605,19 @@
           <t>TUI scroll/vterm</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>9697f5ee</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>Pane::clamped_scroll_offset() + render uses it + down-scroll clamp; test clamped_scroll_offset_clamps_stale_offset_audit2_017; pane 17 + render 76 green</t>
         </is>
       </c>
     </row>
@@ -11494,9 +11642,19 @@
           <t>docs</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>2b3d3a1b</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>USAGE.md: real bins, in-process supervision, dropped dead commands + --detached-&gt;--foreground</t>
         </is>
       </c>
     </row>
@@ -11521,9 +11679,19 @@
           <t>docs</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>2b3d3a1b</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>USAGE.md keybind tables synced to keybinds.rs</t>
         </is>
       </c>
     </row>
@@ -11548,9 +11716,19 @@
           <t>docs</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>2b3d3a1b</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>removed dead AGEND_TURN_SENTINEL_SHADOW from env-vars.md (task.duration sub-item dropped in adjudication)</t>
         </is>
       </c>
     </row>

--- a/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
+++ b/docs/audit/agend-terminal-user-story-feature-tracker.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit2 Tracker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression 2026-06-29" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Stories'!$A$1:$P$108</definedName>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -108,6 +109,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11116,12 +11120,12 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>0013c88e</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>operator gate blocks agent config-set of safety keys (progress_mode/idle_watchdog/hang_auto_recovery/usage_limit) in all modes; test + operator_gate 14 green</t>
         </is>
@@ -11437,12 +11441,12 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>26f960ca</t>
+          <t>a32c6f69</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>set() file-locked + store::atomic_write; runtime_config 15 green</t>
+          <t>atomic_write+flock; REVIEW-HARDENED: disk-base read under lock (true cross-process correctness); test set_uses_disk_base_preserves_concurrent_key; runtime_config 16 green</t>
         </is>
       </c>
     </row>
@@ -11474,12 +11478,12 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>59d13098</t>
+          <t>a32c6f69</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>per-digest flock in stage_filtered_source; digest path + GC unchanged; skills 31 green</t>
+          <t>per-digest flock; REVIEW-HARDENED: cleanup_stale_stages now reaps stale .lock files; skills 31 green</t>
         </is>
       </c>
     </row>
@@ -11729,6 +11733,274 @@
       <c r="G22" s="0" t="inlineStr">
         <is>
           <t>removed dead AGEND_TURN_SENTINEL_SHADOW from env-vars.md (task.duration sub-item dropped in adjudication)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="2" min="1" max="1"/>
+    <col width="28" customWidth="1" style="2" min="2" max="2"/>
+    <col width="34" customWidth="1" style="2" min="3" max="3"/>
+    <col width="70" customWidth="1" style="2" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Test surface</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Binary unit suite (cargo test --bin)</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>REAL git (/usr/bin/git)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>4593 passed / 0 failed / 13 ignored</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>authoritative no-regression signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Binary unit suite</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>agend-git SHIM on PATH</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>4502 passed / 91 failed</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>91 failures are ALL git/worktree tests blocked by the fleet shim — environment artifact, NOT a code regression (untouched code; pass under real git)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Library unit tests (cargo test --lib)</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>25 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Integration: cli_smoke</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>8 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>end-to-end CLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Invariant: atomic_write_invariant</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>relevant to 012/015</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Invariant: core_mutex_invariant</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>1 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>relevant to new locks</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Invariant: block_on_runtime_guard_invariant</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Invariant: anti_pattern_invariant</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>11 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Invariant: cargo_include_invariant</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>3 passed / 0 failed</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Adversarial diff review (16→17 commits)</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>independent agent</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>2 findings, both fixed</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>012 cross-process base re-read; 013 .lock GC reap — re-tested green</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>clippy (unwrap_used=deny)</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>REAL git</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>0 warnings / 0 errors (EXIT 0)</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>unwrap_used=deny passes; no unwrap/expect/panic added in production code</t>
         </is>
       </c>
     </row>
